--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N54_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.62466118891126</v>
+        <v>3.351507443198081</v>
       </c>
       <c r="D2" t="n">
-        <v>20.43956005392559</v>
+        <v>3.321428508762909</v>
       </c>
       <c r="E2" t="n">
-        <v>9.568941076669592</v>
+        <v>1.554952924958809</v>
       </c>
       <c r="F2" t="n">
-        <v>9.717633626461321</v>
+        <v>1.579115464299965</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.42496748190919</v>
+        <v>7.381557215810244</v>
       </c>
       <c r="D3" t="n">
-        <v>45.32106774233157</v>
+        <v>7.364673508128881</v>
       </c>
       <c r="E3" t="n">
-        <v>9.568941076669592</v>
+        <v>1.554952924958809</v>
       </c>
       <c r="F3" t="n">
-        <v>9.717633626461321</v>
+        <v>1.579115464299965</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.98993696362903</v>
+        <v>4.223364756589717</v>
       </c>
       <c r="D4" t="n">
-        <v>25.79497707225461</v>
+        <v>4.191683774241374</v>
       </c>
       <c r="E4" t="n">
-        <v>9.568941076669592</v>
+        <v>1.554952924958809</v>
       </c>
       <c r="F4" t="n">
-        <v>9.717633626461321</v>
+        <v>1.579115464299965</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.0322519788697</v>
+        <v>4.717740946566326</v>
       </c>
       <c r="D5" t="n">
-        <v>28.86653756018982</v>
+        <v>4.690812353530846</v>
       </c>
       <c r="E5" t="n">
-        <v>9.568941076669592</v>
+        <v>1.554952924958809</v>
       </c>
       <c r="F5" t="n">
-        <v>9.717633626461321</v>
+        <v>1.579115464299965</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.88646851825608</v>
+        <v>5.669051134216613</v>
       </c>
       <c r="D6" t="n">
-        <v>34.91342775906282</v>
+        <v>5.673432010847709</v>
       </c>
       <c r="E6" t="n">
-        <v>9.568941076669592</v>
+        <v>1.554952924958809</v>
       </c>
       <c r="F6" t="n">
-        <v>9.717633626461321</v>
+        <v>1.579115464299965</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.25392034505528</v>
+        <v>6.541262056071483</v>
       </c>
       <c r="D7" t="n">
-        <v>40.37938396036647</v>
+        <v>6.561649893559551</v>
       </c>
       <c r="E7" t="n">
-        <v>9.568941076669592</v>
+        <v>1.554952924958809</v>
       </c>
       <c r="F7" t="n">
-        <v>9.717633626461321</v>
+        <v>1.579115464299965</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.6432045021394</v>
+        <v>2.379520731597652</v>
       </c>
       <c r="D8" t="n">
-        <v>14.40669042961047</v>
+        <v>2.341087194811701</v>
       </c>
       <c r="E8" t="n">
-        <v>9.568941076669592</v>
+        <v>1.554952924958809</v>
       </c>
       <c r="F8" t="n">
-        <v>9.717633626461321</v>
+        <v>1.579115464299965</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.94079854038107</v>
+        <v>2.915379762811924</v>
       </c>
       <c r="D9" t="n">
-        <v>18.09431354956196</v>
+        <v>2.940325951803819</v>
       </c>
       <c r="E9" t="n">
-        <v>9.568941076669592</v>
+        <v>1.554952924958809</v>
       </c>
       <c r="F9" t="n">
-        <v>9.717633626461321</v>
+        <v>1.579115464299965</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.60934619224596</v>
+        <v>6.111518756239969</v>
       </c>
       <c r="D10" t="n">
-        <v>37.51535065723704</v>
+        <v>6.096244481801018</v>
       </c>
       <c r="E10" t="n">
-        <v>9.568941076669592</v>
+        <v>1.554952924958809</v>
       </c>
       <c r="F10" t="n">
-        <v>9.717633626461321</v>
+        <v>1.579115464299965</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.09561052971441</v>
+        <v>4.078036711078592</v>
       </c>
       <c r="D11" t="n">
-        <v>25.1019602307606</v>
+        <v>4.079068537498597</v>
       </c>
       <c r="E11" t="n">
-        <v>9.568941076669592</v>
+        <v>1.554952924958809</v>
       </c>
       <c r="F11" t="n">
-        <v>9.717633626461321</v>
+        <v>1.579115464299965</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.11130885718335</v>
+        <v>4.405587689292294</v>
       </c>
       <c r="D12" t="n">
-        <v>27.3372013502788</v>
+        <v>4.442295219420306</v>
       </c>
       <c r="E12" t="n">
-        <v>9.568941076669592</v>
+        <v>1.554952924958809</v>
       </c>
       <c r="F12" t="n">
-        <v>9.717633626461321</v>
+        <v>1.579115464299965</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>37.63098208366556</v>
+        <v>6.115034588595655</v>
       </c>
       <c r="D13" t="n">
-        <v>37.85049747088998</v>
+        <v>6.150705839019621</v>
       </c>
       <c r="E13" t="n">
-        <v>9.568941076669592</v>
+        <v>1.554952924958809</v>
       </c>
       <c r="F13" t="n">
-        <v>9.717633626461321</v>
+        <v>1.579115464299965</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>36.21649823706386</v>
+        <v>5.885180963522878</v>
       </c>
       <c r="D14" t="n">
-        <v>36.40678919838196</v>
+        <v>5.916103244737069</v>
       </c>
       <c r="E14" t="n">
-        <v>9.568941076669592</v>
+        <v>1.554952924958809</v>
       </c>
       <c r="F14" t="n">
-        <v>9.717633626461321</v>
+        <v>1.579115464299965</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>42.13813482455441</v>
+        <v>6.847446908990091</v>
       </c>
       <c r="D15" t="n">
-        <v>42.20885936950012</v>
+        <v>6.858939647543769</v>
       </c>
       <c r="E15" t="n">
-        <v>9.568941076669592</v>
+        <v>1.554952924958809</v>
       </c>
       <c r="F15" t="n">
-        <v>9.717633626461321</v>
+        <v>1.579115464299965</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>17.80312498643878</v>
+        <v>2.893007810296301</v>
       </c>
       <c r="D16" t="n">
-        <v>16.74771716858926</v>
+        <v>2.721504039895755</v>
       </c>
       <c r="E16" t="n">
-        <v>9.568941076669592</v>
+        <v>1.554952924958809</v>
       </c>
       <c r="F16" t="n">
-        <v>9.717633626461321</v>
+        <v>1.579115464299965</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>41.89148747368616</v>
+        <v>6.807366714474002</v>
       </c>
       <c r="D17" t="n">
-        <v>42.05907758420673</v>
+        <v>6.834600107433594</v>
       </c>
       <c r="E17" t="n">
-        <v>9.568941076669592</v>
+        <v>1.554952924958809</v>
       </c>
       <c r="F17" t="n">
-        <v>9.717633626461321</v>
+        <v>1.579115464299965</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
